--- a/Unity/Assets/Config/Excel/EquipIdentifyConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipIdentifyConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22110" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EquipIdentifyProto" sheetId="1" r:id="rId1"/>
@@ -29,58 +29,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Administrator</author>
     <author>LDYQ</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:
-1:技能特效
-2.场景特效</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-3.ui特效</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0 表示跟随
-1 表示不跟随碰撞体</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="1">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,21 +59,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>职业</t>
-  </si>
-  <si>
-    <t>特效类型</t>
-  </si>
-  <si>
-    <t>特效是否跟随绑定</t>
   </si>
   <si>
     <t>装备类型</t>
@@ -134,12 +77,6 @@
   </si>
   <si>
     <t>occ</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>IfFollowCollider</t>
   </si>
   <si>
     <t>StdMode</t>
@@ -6974,95 +6911,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="C1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="9" style="5"/>
     <col min="3" max="3" width="11.5" style="5" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="40.5" customWidth="1"/>
-    <col min="8" max="9" width="36.375" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="5"/>
+    <col min="5" max="5" width="40.5" customWidth="1"/>
+    <col min="6" max="7" width="36.375" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14.25"/>
-    <row r="2" spans="3:9">
-      <c r="D2" s="5" t="s">
+    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="s">
+    </row>
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
-      <c r="C4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+    </row>
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
-      <c r="C5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="6" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
       <c r="C6" s="8">
         <v>1</v>
       </c>
@@ -7070,45 +6982,33 @@
         <v>1</v>
       </c>
       <c r="E6" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
         <v>3000</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>16</v>
+      <c r="G6" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="3:9">
+    <row r="7" s="4" customFormat="1" ht="38" customHeight="1" spans="3:7">
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="8">
         <v>1</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="F7" s="8">
         <v>3000</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>16</v>
+      <c r="G7" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="8" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
       <c r="C8" s="8">
         <v>3</v>
       </c>
@@ -7116,45 +7016,33 @@
         <v>2</v>
       </c>
       <c r="E8" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
         <v>3000</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>16</v>
+      <c r="G8" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" ht="38" customHeight="1" spans="3:9">
+    <row r="9" s="4" customFormat="1" ht="38" customHeight="1" spans="3:7">
       <c r="C9" s="3">
         <v>4</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="F9" s="8">
         <v>3000</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>16</v>
+      <c r="G9" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:9">
+    <row r="10" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:7">
       <c r="C10" s="8">
         <v>5</v>
       </c>
@@ -7162,42 +7050,30 @@
         <v>3</v>
       </c>
       <c r="E10" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
         <v>3000</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>16</v>
+      <c r="G10" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" ht="38" customHeight="1" spans="3:9">
+    <row r="11" s="4" customFormat="1" ht="38" customHeight="1" spans="3:7">
       <c r="C11" s="3">
         <v>6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="8">
         <v>1</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="F11" s="8">
         <v>3000</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>16</v>
+      <c r="G11" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
